--- a/frontend/public/Template_Carteira_Sevilha.xlsx
+++ b/frontend/public/Template_Carteira_Sevilha.xlsx
@@ -176,7 +176,7 @@
       <text>
         <t>Campo #1 — MESTRE
 Entra no cálculo: informativo, não pontua
-Formato: Data
+Formato: mês no padrão AAAA-MM (ex.: 2026-08)
 Informe a data em que o escritório iniciou efetivamente o atendimento operacional do cliente, e não apenas a data de assinatura do contrato.</t>
       </text>
     </comment>
@@ -184,7 +184,7 @@
       <text>
         <t>Campo #2 — MESTRE
 Entra no cálculo: informativo, não pontua
-Formato: Data
+Formato: mês no padrão AAAA-MM (ex.: 2026-08)
 Informe o mês de referência ao qual os dados do cadastro se aplicam, no formato AAAA-MM.</t>
       </text>
     </comment>
@@ -489,7 +489,7 @@
         <t>Campo #33 — CONTÁBIL
 Entra no cálculo: informativo, não pontua
 Pilar: Atraso / desempenho
-Formato: Data
+Formato: mês no padrão AAAA-MM (ex.: 2026-08)
 Informe a competência mais recente cuja conciliação esteja integralmente concluída; não considere mês parcialmente conciliado.</t>
       </text>
     </comment>

--- a/frontend/public/Template_Carteira_Sevilha.xlsx
+++ b/frontend/public/Template_Carteira_Sevilha.xlsx
@@ -329,7 +329,7 @@
       <text>
         <t>Campo #17 — FISCAL
 Entra no cálculo: informativo, não pontua
-Formato: Base de Equipe
+Escreva o nome como está em Estrutura &gt; Equipe. A pessoa precisa estar cadastrada antes da importação — nome que não bate deixa a frente sem responsável e aparece no aviso.
 Informe a pessoa que responde prioritariamente pela carteira deste cliente no ciclo; quando houver atuação compartilhada, use o titular formalmente definido.</t>
       </text>
     </comment>
@@ -337,7 +337,7 @@
       <text>
         <t>Campo #18 — FISCAL
 Entra no cálculo: informativo, não pontua
-Formato: Base de Equipe
+Escreva o nome como está em Estrutura &gt; Equipe. A pessoa precisa estar cadastrada antes da importação — nome que não bate deixa a frente sem responsável e aparece no aviso.
 Informe apenas quando houver uma segunda pessoa formalmente designada para apoio, cobertura ou corresponsabilidade; caso contrário, deixe em branco.</t>
       </text>
     </comment>
@@ -422,7 +422,7 @@
       <text>
         <t>Campo #26 — CONTÁBIL
 Entra no cálculo: informativo, não pontua
-Formato: Base de Equipe
+Escreva o nome como está em Estrutura &gt; Equipe. A pessoa precisa estar cadastrada antes da importação — nome que não bate deixa a frente sem responsável e aparece no aviso.
 Informe a pessoa que responde prioritariamente pela carteira deste cliente no ciclo; quando houver atuação compartilhada, use o titular formalmente definido.</t>
       </text>
     </comment>
@@ -430,7 +430,7 @@
       <text>
         <t>Campo #27 — CONTÁBIL
 Entra no cálculo: informativo, não pontua
-Formato: Base de Equipe
+Escreva o nome como está em Estrutura &gt; Equipe. A pessoa precisa estar cadastrada antes da importação — nome que não bate deixa a frente sem responsável e aparece no aviso.
 Informe apenas quando houver uma segunda pessoa formalmente designada para apoio, cobertura ou corresponsabilidade; caso contrário, deixe em branco.</t>
       </text>
     </comment>
@@ -544,7 +544,7 @@
       <text>
         <t>Campo #38 — PESSOAL
 Entra no cálculo: informativo, não pontua
-Formato: Base de Equipe
+Escreva o nome como está em Estrutura &gt; Equipe. A pessoa precisa estar cadastrada antes da importação — nome que não bate deixa a frente sem responsável e aparece no aviso.
 Informe a pessoa que responde prioritariamente pela carteira deste cliente no ciclo; quando houver atuação compartilhada, use o titular formalmente definido.</t>
       </text>
     </comment>
@@ -552,7 +552,7 @@
       <text>
         <t>Campo #39 — PESSOAL
 Entra no cálculo: informativo, não pontua
-Formato: Base de Equipe
+Escreva o nome como está em Estrutura &gt; Equipe. A pessoa precisa estar cadastrada antes da importação — nome que não bate deixa a frente sem responsável e aparece no aviso.
 Informe apenas quando houver uma segunda pessoa formalmente designada para apoio, cobertura ou corresponsabilidade; caso contrário, deixe em branco.</t>
       </text>
     </comment>
